--- a/docs/pension_data_combined_2026-06-11.xlsx
+++ b/docs/pension_data_combined_2026-06-11.xlsx
@@ -1335,9 +1335,6 @@
       <c r="C54" t="n">
         <v>1.5346</v>
       </c>
-      <c r="D54" t="n">
-        <v>366043587.79</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">

--- a/docs/pension_data_combined_2026-06-11.xlsx
+++ b/docs/pension_data_combined_2026-06-11.xlsx
@@ -1299,9 +1299,6 @@
       <c r="C52" t="n">
         <v>2.1405</v>
       </c>
-      <c r="D52" t="n">
-        <v>494810052.66</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1334,6 +1331,9 @@
       </c>
       <c r="C54" t="n">
         <v>1.5346</v>
+      </c>
+      <c r="D54" t="n">
+        <v>366043587.79</v>
       </c>
     </row>
     <row r="55">

--- a/docs/pension_data_combined_2026-06-11.xlsx
+++ b/docs/pension_data_combined_2026-06-11.xlsx
@@ -1263,9 +1263,6 @@
       <c r="C50" t="n">
         <v>2.1241</v>
       </c>
-      <c r="D50" t="n">
-        <v>268576130.89</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1298,6 +1295,9 @@
       </c>
       <c r="C52" t="n">
         <v>2.1405</v>
+      </c>
+      <c r="D52" t="n">
+        <v>494810052.66</v>
       </c>
     </row>
     <row r="53">

--- a/docs/pension_data_combined_2026-06-11.xlsx
+++ b/docs/pension_data_combined_2026-06-11.xlsx
@@ -1263,6 +1263,9 @@
       <c r="C50" t="n">
         <v>2.1241</v>
       </c>
+      <c r="D50" t="n">
+        <v>268576130.89</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
